--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.76557864191827</v>
+        <v>6.136906529311719</v>
       </c>
       <c r="D2" t="n">
-        <v>35.55401793473178</v>
+        <v>5.777527914393914</v>
       </c>
       <c r="E2" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F2" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.9180956599664</v>
+        <v>5.349190544744541</v>
       </c>
       <c r="D3" t="n">
-        <v>33.77325127737805</v>
+        <v>5.488153332573933</v>
       </c>
       <c r="E3" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F3" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.1719547781467</v>
+        <v>3.440442651448839</v>
       </c>
       <c r="D4" t="n">
-        <v>20.329323720769</v>
+        <v>3.303515104624963</v>
       </c>
       <c r="E4" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F4" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.17962001301539</v>
+        <v>6.204188252115002</v>
       </c>
       <c r="D5" t="n">
-        <v>38.94379452340961</v>
+        <v>6.328366610054061</v>
       </c>
       <c r="E5" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F5" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.222294866238748</v>
+        <v>1.011122915763797</v>
       </c>
       <c r="D6" t="n">
-        <v>7.524952984992282</v>
+        <v>1.222804860061246</v>
       </c>
       <c r="E6" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F6" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.38642743292647</v>
+        <v>7.537794457850552</v>
       </c>
       <c r="D7" t="n">
-        <v>19.09657065171655</v>
+        <v>3.10319273090394</v>
       </c>
       <c r="E7" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F7" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.50755035428168</v>
+        <v>4.794976932570773</v>
       </c>
       <c r="D8" t="n">
-        <v>28.52123735574816</v>
+        <v>4.634701070309076</v>
       </c>
       <c r="E8" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F8" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.30806049814195</v>
+        <v>4.600059830948067</v>
       </c>
       <c r="D9" t="n">
-        <v>27.46995449191036</v>
+        <v>4.463867604935434</v>
       </c>
       <c r="E9" t="n">
-        <v>11.45989250230543</v>
+        <v>1.862232531624632</v>
       </c>
       <c r="F9" t="n">
-        <v>9.667035994934704</v>
+        <v>1.570893349176889</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
